--- a/output/pdf_financials_xlsx/MNG.xlsx
+++ b/output/pdf_financials_xlsx/MNG.xlsx
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.136645</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.115881</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.112531</v>
       </c>
     </row>
     <row r="93">
@@ -3176,7 +3176,11 @@
           <t>Share-based payment reserve 9</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -3695,7 +3699,11 @@
           <t>Share-based payment reserve 8 115,881</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>0.136645</v>
       </c>

--- a/output/pdf_financials_xlsx/MNG.xlsx
+++ b/output/pdf_financials_xlsx/MNG.xlsx
@@ -982,13 +982,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.085207</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.001716</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.043173</v>
       </c>
     </row>
     <row r="35">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.085207</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.001716</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.043173</v>
       </c>
     </row>
     <row r="37">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.099347</v>
+        <v>0.01414</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.004402</v>
+        <v>0.002686</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.083093</v>
+        <v>0.03992</v>
       </c>
     </row>
     <row r="49">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3323,7 +3323,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">

--- a/output/pdf_financials_xlsx/MNG.xlsx
+++ b/output/pdf_financials_xlsx/MNG.xlsx
@@ -1468,13 +1468,13 @@
         </is>
       </c>
       <c r="B64" s="3" t="n">
-        <v>0</v>
+        <v>0.102578</v>
       </c>
       <c r="C64" s="3" t="n">
-        <v>0</v>
+        <v>0.066515</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>0.082619</v>
       </c>
     </row>
     <row r="65">
@@ -1516,13 +1516,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.03924</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.039546</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.049221</v>
       </c>
     </row>
     <row r="68">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.000248</v>
       </c>
     </row>
     <row r="111">
@@ -2542,10 +2542,8 @@
       <c r="C130" s="3" t="n">
         <v>0.061841</v>
       </c>
-      <c r="D130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D130" s="3" t="n">
+        <v>0.001716</v>
       </c>
     </row>
     <row r="131">
@@ -2592,10 +2590,8 @@
       <c r="C133" s="3" t="n">
         <v>0.001716</v>
       </c>
-      <c r="D133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D133" s="3" t="n">
+        <v>0.043173</v>
       </c>
     </row>
     <row r="134">
@@ -3935,7 +3931,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -4381,7 +4381,11 @@
           <t>Cash at beginning of the year</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -4410,7 +4414,11 @@
           <t>Cash at end of the year</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
